--- a/Bug_Report.xlsx
+++ b/Bug_Report.xlsx
@@ -193,8 +193,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,233 +530,239 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="59.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="33.75" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" ht="47.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.75">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" ht="204.75">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75">
-      <c r="A3" t="s">
+    <row r="3" spans="1:12" ht="204.75">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75">
-      <c r="A4" t="s">
+    <row r="4" spans="1:12" ht="299.25">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75">
-      <c r="A5" t="s">
+    <row r="5" spans="1:12" ht="299.25">
+      <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" ht="315">
+      <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
